--- a/StructureDefinition-SEEHDSLMRequestActivitiesV10.xlsx
+++ b/StructureDefinition-SEEHDSLMRequestActivitiesV10.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMRequestActivitiesV10.xlsx
+++ b/StructureDefinition-SEEHDSLMRequestActivitiesV10.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,8 +260,8 @@
     <t>requestActivity</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
+    <t>getrequestactivities1-request-id:Minst ett av senderRequestId och receiverRequestId ska anges {senderRequestId.exists() or receiverRequestId.exists()}
+getrequestactivities1-issued-by-unit:Minst ett av requestIssuedByOrganizationalUnitId och requestIssuedByOrganizationalUnitDescription ska anges {requestIssuedByOrganizationalUnitId.exists() or requestIssuedByOrganizationalUnitDescription.exists()}getrequestactivities1-receiving-unit:Minst ett av receivingOrganizationalUnitId och receivingOrganizationalUnitDescription ska anges {receivingOrganizationalUnitId.exists() or receivingOrganizationalUnitDescription.exists()}getrequestactivities1-status-code:typeOfRequest ska vara 1, 2, 4 eller 10 och statusCode ska vara en av de koder som är tillåtna för remisstypen (VER-005) {(typeOfRequest.value = '1' and statusCode.value in ('20' | '30' | '90' | '126' | '130' | '136' | '140')) or (typeOfRequest.value = '2' and statusCode.value in ('20' | '30' | '126' | '130' | '136' | '140')) or (typeOfRequest.value = '4' and statusCode.value in ('20' | '30' | '90' | '130' | '140')) or (typeOfRequest.value = '10' and statusCode.value in ('20' | '30' | '90' | '140'))}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMRequestActivitiesV10.requestActivity.id</t>

--- a/StructureDefinition-SEEHDSLMRequestActivitiesV10.xlsx
+++ b/StructureDefinition-SEEHDSLMRequestActivitiesV10.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMRequestActivitiesV10.xlsx
+++ b/StructureDefinition-SEEHDSLMRequestActivitiesV10.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
